--- a/docs/qmd/chapter_1/downloads/receiver_log_complete.xlsx
+++ b/docs/qmd/chapter_1/downloads/receiver_log_complete.xlsx
@@ -370,7 +370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:AX178"/>
+  <dimension ref="A1:AU178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -566,60 +566,45 @@
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>station_power_dep</t>
+          <t>tag_test_perf_dep</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>wifi_dep</t>
+          <t>tag_test_perf_success_dep</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>wifi_notes_dep</t>
+          <t>tag_test_notes_dep</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>tag_test_perf_dep</t>
+          <t>station_power_departure</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>tag_test_perf_success_dep</t>
+          <t>wifi_departure</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>tag_test_notes_dep</t>
+          <t>wifi_notes_departure</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>station_power_departure</t>
+          <t>receiver_replacement_sg_version</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>wifi_departure</t>
+          <t>sg_lon</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
-        <is>
-          <t>wifi_notes_departure</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>receiver_replacement_sg_version</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>sg_lon</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
         <is>
           <t>sg_lat</t>
         </is>
@@ -774,18 +759,22 @@
       <c r="AL2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN2" t="e">
-        <v>#N/A</v>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO2" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -796,26 +785,13 @@
       <c r="AR2" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV2" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW2">
+      <c r="AS2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT2">
         <v>151.969829593599</v>
       </c>
-      <c r="AX2">
+      <c r="AU2">
         <v>-32.690586398903</v>
       </c>
     </row>
@@ -954,18 +930,22 @@
       <c r="AL3" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN3" t="e">
-        <v>#N/A</v>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO3" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -976,26 +956,13 @@
       <c r="AR3" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV3" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW3">
+      <c r="AS3" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT3">
         <v>151.96638388524</v>
       </c>
-      <c r="AX3">
+      <c r="AU3">
         <v>-32.704262001199</v>
       </c>
     </row>
@@ -1147,18 +1114,22 @@
       <c r="AL4" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN4" t="e">
-        <v>#N/A</v>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO4" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1169,26 +1140,13 @@
       <c r="AR4" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW4">
+      <c r="AS4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT4">
         <v>151.96638388524</v>
       </c>
-      <c r="AX4">
+      <c r="AU4">
         <v>-32.704262001199</v>
       </c>
     </row>
@@ -1329,18 +1287,22 @@
       <c r="AL5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN5" t="e">
-        <v>#N/A</v>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO5" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1351,26 +1313,13 @@
       <c r="AR5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW5">
+      <c r="AS5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT5">
         <v>151.779273244043</v>
       </c>
-      <c r="AX5">
+      <c r="AU5">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -1524,8 +1473,10 @@
       <c r="AL6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM6" t="e">
-        <v>#N/A</v>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="AN6" t="e">
         <v>#N/A</v>
@@ -1535,7 +1486,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="AQ6" t="e">
@@ -1544,24 +1495,13 @@
       <c r="AR6" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="AT6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW6">
+      <c r="AS6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT6">
         <v>151.806500367329</v>
       </c>
-      <c r="AX6">
+      <c r="AU6">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -1712,8 +1652,10 @@
       <c r="AL7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM7" t="e">
-        <v>#N/A</v>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="AN7" t="e">
         <v>#N/A</v>
@@ -1723,7 +1665,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="AQ7" t="e">
@@ -1732,24 +1674,13 @@
       <c r="AR7" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="AT7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV7" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW7">
+      <c r="AS7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT7">
         <v>151.681010702398</v>
       </c>
-      <c r="AX7">
+      <c r="AU7">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -1896,8 +1827,10 @@
       <c r="AL8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM8" t="e">
-        <v>#N/A</v>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="AN8" t="e">
         <v>#N/A</v>
@@ -1907,35 +1840,24 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AQ8" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR8" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AU8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW8">
+      <c r="AS8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT8">
         <v>151.681010702398</v>
       </c>
-      <c r="AX8">
+      <c r="AU8">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -2087,18 +2009,22 @@
       <c r="AL9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN9" t="e">
-        <v>#N/A</v>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO9" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2109,26 +2035,13 @@
       <c r="AR9" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV9" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW9">
+      <c r="AS9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT9">
         <v>151.713805317914</v>
       </c>
-      <c r="AX9">
+      <c r="AU9">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -2277,18 +2190,22 @@
       <c r="AL10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN10" t="e">
-        <v>#N/A</v>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO10" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2299,26 +2216,13 @@
       <c r="AR10" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV10" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW10">
+      <c r="AS10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT10">
         <v>151.716736464092</v>
       </c>
-      <c r="AX10">
+      <c r="AU10">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -2459,18 +2363,22 @@
           <t>SG-F923RPI3B0B6</t>
         </is>
       </c>
-      <c r="AM11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN11" t="e">
-        <v>#N/A</v>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AO11" t="e">
         <v>#N/A</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>on</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2483,26 +2391,13 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU11" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
           <t>sg_version_1</t>
         </is>
       </c>
-      <c r="AW11">
+      <c r="AT11">
         <v>151.719270560305</v>
       </c>
-      <c r="AX11">
+      <c r="AU11">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -2643,51 +2538,42 @@
       <c r="AL12" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
         <is>
           <t>Detected consistently by ant2 and ant3
 How to tell which is which is which in the field? I.e which is directional vs. Omni</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV12" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW12">
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AR12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT12">
         <v>151.757296984696</v>
       </c>
-      <c r="AX12">
+      <c r="AU12">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -2857,24 +2743,24 @@
           <t>SG-CE0DRPI43C5E</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP13" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ13" t="e">
-        <v>#N/A</v>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR13" t="e">
         <v>#N/A</v>
@@ -2882,19 +2768,10 @@
       <c r="AS13" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV13" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW13">
+      <c r="AT13">
         <v>151.969829593599</v>
       </c>
-      <c r="AX13">
+      <c r="AU13">
         <v>-32.690586398903</v>
       </c>
     </row>
@@ -3051,35 +2928,26 @@
       <c r="AO14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ14" t="e">
-        <v>#N/A</v>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR14" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV14" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW14">
+      <c r="AS14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT14">
         <v>151.681010702398</v>
       </c>
-      <c r="AX14">
+      <c r="AU14">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -3231,35 +3099,26 @@
       <c r="AO15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ15" t="e">
-        <v>#N/A</v>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV15" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW15">
+      <c r="AS15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT15">
         <v>151.713805317914</v>
       </c>
-      <c r="AX15">
+      <c r="AU15">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -3413,35 +3272,26 @@
       <c r="AO16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ16" t="e">
-        <v>#N/A</v>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR16" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV16" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW16">
+      <c r="AS16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT16">
         <v>151.716736464092</v>
       </c>
-      <c r="AX16">
+      <c r="AU16">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -3595,35 +3445,26 @@
       <c r="AO17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ17" t="e">
-        <v>#N/A</v>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="AR17" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AU17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV17" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW17">
+      <c r="AS17" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT17">
         <v>151.719270560305</v>
       </c>
-      <c r="AX17">
+      <c r="AU17">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -3795,35 +3636,26 @@
       <c r="AO18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ18" t="e">
-        <v>#N/A</v>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR18" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV18" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW18">
+      <c r="AS18" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT18">
         <v>152.137455181598</v>
       </c>
-      <c r="AX18">
+      <c r="AU18">
         <v>-32.684190312235</v>
       </c>
     </row>
@@ -3973,35 +3805,26 @@
       <c r="AO19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AP19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ19" t="e">
-        <v>#N/A</v>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR19" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AU19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV19" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW19">
+      <c r="AS19" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT19">
         <v>151.757296984696</v>
       </c>
-      <c r="AX19">
+      <c r="AU19">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -4153,19 +3976,10 @@
       <c r="AS20" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV20" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW20">
+      <c r="AT20">
         <v>151.96638388524</v>
       </c>
-      <c r="AX20">
+      <c r="AU20">
         <v>-32.704262001199</v>
       </c>
     </row>
@@ -4310,24 +4124,24 @@
           <t>SG-7F7ERPI31522</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AM21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP21" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ21" t="e">
-        <v>#N/A</v>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR21" t="e">
         <v>#N/A</v>
@@ -4335,19 +4149,10 @@
       <c r="AS21" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV21" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW21">
+      <c r="AT21">
         <v>151.743343598915</v>
       </c>
-      <c r="AX21">
+      <c r="AU21">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -4497,19 +4302,10 @@
       <c r="AS22" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV22" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW22">
+      <c r="AT22">
         <v>151.96638388524</v>
       </c>
-      <c r="AX22">
+      <c r="AU22">
         <v>-32.704262001199</v>
       </c>
     </row>
@@ -4644,24 +4440,24 @@
       <c r="AL23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AM23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP23" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ23" t="e">
-        <v>#N/A</v>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR23" t="e">
         <v>#N/A</v>
@@ -4669,19 +4465,10 @@
       <c r="AS23" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW23">
+      <c r="AT23">
         <v>151.779273244043</v>
       </c>
-      <c r="AX23">
+      <c r="AU23">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -4816,24 +4603,24 @@
       <c r="AL24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP24" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ24" t="e">
-        <v>#N/A</v>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR24" t="e">
         <v>#N/A</v>
@@ -4841,19 +4628,10 @@
       <c r="AS24" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV24" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW24">
+      <c r="AT24">
         <v>151.806500367329</v>
       </c>
-      <c r="AX24">
+      <c r="AU24">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -4988,24 +4766,24 @@
       <c r="AL25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP25" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" t="e">
-        <v>#N/A</v>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR25" t="e">
         <v>#N/A</v>
@@ -5013,19 +4791,10 @@
       <c r="AS25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25">
+      <c r="AT25">
         <v>151.713805317914</v>
       </c>
-      <c r="AX25">
+      <c r="AU25">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -5160,24 +4929,24 @@
       <c r="AL26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AM26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ26" t="e">
-        <v>#N/A</v>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR26" t="e">
         <v>#N/A</v>
@@ -5185,19 +4954,10 @@
       <c r="AS26" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW26">
+      <c r="AT26">
         <v>151.716736464092</v>
       </c>
-      <c r="AX26">
+      <c r="AU26">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -5332,24 +5092,24 @@
       <c r="AL27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AM27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP27" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ27" t="e">
-        <v>#N/A</v>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR27" t="e">
         <v>#N/A</v>
@@ -5357,19 +5117,10 @@
       <c r="AS27" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV27" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW27">
+      <c r="AT27">
         <v>151.719270560305</v>
       </c>
-      <c r="AX27">
+      <c r="AU27">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -5508,24 +5259,24 @@
       <c r="AL28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AM28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO28" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP28" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ28" t="e">
-        <v>#N/A</v>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR28" t="e">
         <v>#N/A</v>
@@ -5533,19 +5284,10 @@
       <c r="AS28" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV28" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW28">
+      <c r="AT28">
         <v>151.779273244043</v>
       </c>
-      <c r="AX28">
+      <c r="AU28">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -5684,24 +5426,24 @@
       <c r="AL29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AM29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP29" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ29" t="e">
-        <v>#N/A</v>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR29" t="e">
         <v>#N/A</v>
@@ -5709,19 +5451,10 @@
       <c r="AS29" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV29" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW29">
+      <c r="AT29">
         <v>151.806500367329</v>
       </c>
-      <c r="AX29">
+      <c r="AU29">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -5871,19 +5604,10 @@
       <c r="AS30" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV30" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW30">
+      <c r="AT30">
         <v>151.779273244043</v>
       </c>
-      <c r="AX30">
+      <c r="AU30">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -6018,24 +5742,24 @@
       <c r="AL31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AM31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP31" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ31" t="e">
-        <v>#N/A</v>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR31" t="e">
         <v>#N/A</v>
@@ -6043,19 +5767,10 @@
       <c r="AS31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW31">
+      <c r="AT31">
         <v>151.681010702398</v>
       </c>
-      <c r="AX31">
+      <c r="AU31">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -6190,24 +5905,24 @@
       <c r="AL32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO32" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP32" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ32" t="e">
-        <v>#N/A</v>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR32" t="e">
         <v>#N/A</v>
@@ -6215,19 +5930,10 @@
       <c r="AS32" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV32" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW32">
+      <c r="AT32">
         <v>151.713805317914</v>
       </c>
-      <c r="AX32">
+      <c r="AU32">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -6376,24 +6082,24 @@
       <c r="AL33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP33" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ33" t="e">
-        <v>#N/A</v>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR33" t="e">
         <v>#N/A</v>
@@ -6401,19 +6107,10 @@
       <c r="AS33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW33">
+      <c r="AT33">
         <v>151.716736464092</v>
       </c>
-      <c r="AX33">
+      <c r="AU33">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -6548,24 +6245,24 @@
       <c r="AL34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO34" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP34" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ34" t="e">
-        <v>#N/A</v>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR34" t="e">
         <v>#N/A</v>
@@ -6573,19 +6270,10 @@
       <c r="AS34" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV34" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW34">
+      <c r="AT34">
         <v>151.719270560305</v>
       </c>
-      <c r="AX34">
+      <c r="AU34">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -6735,19 +6423,10 @@
       <c r="AS35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW35">
+      <c r="AT35">
         <v>151.757296984696</v>
       </c>
-      <c r="AX35">
+      <c r="AU35">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -6908,19 +6587,10 @@
       <c r="AS36" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV36" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW36">
+      <c r="AT36">
         <v>151.757296984696</v>
       </c>
-      <c r="AX36">
+      <c r="AU36">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -7083,19 +6753,10 @@
       <c r="AS37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW37">
+      <c r="AT37">
         <v>151.757296984696</v>
       </c>
-      <c r="AX37">
+      <c r="AU37">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -7241,24 +6902,24 @@
       <c r="AL38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AM38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP38" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ38" t="e">
-        <v>#N/A</v>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR38" t="e">
         <v>#N/A</v>
@@ -7266,19 +6927,10 @@
       <c r="AS38" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV38" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW38">
+      <c r="AT38">
         <v>151.806500367329</v>
       </c>
-      <c r="AX38">
+      <c r="AU38">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -7415,24 +7067,24 @@
       <c r="AL39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AM39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO39" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP39" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ39" t="e">
-        <v>#N/A</v>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR39" t="e">
         <v>#N/A</v>
@@ -7440,19 +7092,10 @@
       <c r="AS39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW39">
+      <c r="AT39">
         <v>151.713805317914</v>
       </c>
-      <c r="AX39">
+      <c r="AU39">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -7601,24 +7244,24 @@
       <c r="AL40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AM40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO40" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP40" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ40" t="e">
-        <v>#N/A</v>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR40" t="e">
         <v>#N/A</v>
@@ -7626,19 +7269,10 @@
       <c r="AS40" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV40" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW40">
+      <c r="AT40">
         <v>151.716736464092</v>
       </c>
-      <c r="AX40">
+      <c r="AU40">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -7775,24 +7409,24 @@
       <c r="AL41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AM41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP41" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ41" t="e">
-        <v>#N/A</v>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR41" t="e">
         <v>#N/A</v>
@@ -7800,19 +7434,10 @@
       <c r="AS41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW41">
+      <c r="AT41">
         <v>151.719270560305</v>
       </c>
-      <c r="AX41">
+      <c r="AU41">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -7966,19 +7591,10 @@
       <c r="AS42" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV42" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW42">
+      <c r="AT42">
         <v>151.743343598915</v>
       </c>
-      <c r="AX42">
+      <c r="AU42">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -8130,19 +7746,10 @@
       <c r="AS43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW43">
+      <c r="AT43">
         <v>151.96638388524</v>
       </c>
-      <c r="AX43">
+      <c r="AU43">
         <v>-32.704262001199</v>
       </c>
     </row>
@@ -8298,19 +7905,10 @@
       <c r="AS44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV44" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW44">
+      <c r="AT44">
         <v>151.757296984696</v>
       </c>
-      <c r="AX44">
+      <c r="AU44">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -8465,19 +8063,10 @@
       <c r="AS45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW45">
+      <c r="AT45">
         <v>151.681010702398</v>
       </c>
-      <c r="AX45">
+      <c r="AU45">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -8636,19 +8225,10 @@
       <c r="AS46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW46">
+      <c r="AT46">
         <v>151.806500367329</v>
       </c>
-      <c r="AX46">
+      <c r="AU46">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -8797,24 +8377,24 @@
       <c r="AL47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AM47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO47" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP47" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ47" t="e">
-        <v>#N/A</v>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR47" t="e">
         <v>#N/A</v>
@@ -8822,19 +8402,10 @@
       <c r="AS47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV47" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW47">
+      <c r="AT47">
         <v>151.806500367329</v>
       </c>
-      <c r="AX47">
+      <c r="AU47">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -8995,19 +8566,10 @@
       <c r="AS48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV48" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW48">
+      <c r="AT48">
         <v>151.681010702398</v>
       </c>
-      <c r="AX48">
+      <c r="AU48">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -9167,44 +8729,35 @@
       <c r="AL49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM49" t="inlineStr">
+      <c r="AM49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO49" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP49" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
+      <c r="AQ49" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ49" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR49" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV49" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW49">
+      <c r="AT49">
         <v>151.779273244043</v>
       </c>
-      <c r="AX49">
+      <c r="AU49">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -9355,44 +8908,35 @@
       <c r="AL50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AM50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO50" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP50" t="inlineStr">
         <is>
           <t>removed</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
+      <c r="AQ50" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ50" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR50" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV50" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW50">
+      <c r="AT50">
         <v>151.713805317914</v>
       </c>
-      <c r="AX50">
+      <c r="AU50">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -9527,24 +9071,24 @@
       <c r="AL51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AM51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO51" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP51" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ51" t="e">
-        <v>#N/A</v>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR51" t="e">
         <v>#N/A</v>
@@ -9552,19 +9096,10 @@
       <c r="AS51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV51" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW51">
+      <c r="AT51">
         <v>151.719270560305</v>
       </c>
-      <c r="AX51">
+      <c r="AU51">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -9715,44 +9250,35 @@
       <c r="AL52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AM52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO52" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP52" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AQ52" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ52" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR52" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV52" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW52">
+      <c r="AT52">
         <v>151.743343598915</v>
       </c>
-      <c r="AX52">
+      <c r="AU52">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -9887,24 +9413,24 @@
       <c r="AL53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO53" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP53" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ53" t="e">
-        <v>#N/A</v>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR53" t="e">
         <v>#N/A</v>
@@ -9912,19 +9438,10 @@
       <c r="AS53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV53" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW53">
+      <c r="AT53">
         <v>151.779273244043</v>
       </c>
-      <c r="AX53">
+      <c r="AU53">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -10059,24 +9576,24 @@
       <c r="AL54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO54" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP54" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ54" t="e">
-        <v>#N/A</v>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR54" t="e">
         <v>#N/A</v>
@@ -10084,19 +9601,10 @@
       <c r="AS54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV54" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW54">
+      <c r="AT54">
         <v>151.806500367329</v>
       </c>
-      <c r="AX54">
+      <c r="AU54">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -10229,24 +9737,24 @@
       <c r="AL55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP55" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ55" t="e">
-        <v>#N/A</v>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR55" t="e">
         <v>#N/A</v>
@@ -10254,19 +9762,10 @@
       <c r="AS55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW55">
+      <c r="AT55">
         <v>151.681010702398</v>
       </c>
-      <c r="AX55">
+      <c r="AU55">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -10399,24 +9898,24 @@
       <c r="AL56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP56" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ56" t="e">
-        <v>#N/A</v>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR56" t="e">
         <v>#N/A</v>
@@ -10424,19 +9923,10 @@
       <c r="AS56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW56">
+      <c r="AT56">
         <v>151.713805317914</v>
       </c>
-      <c r="AX56">
+      <c r="AU56">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -10594,19 +10084,10 @@
       <c r="AS57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV57" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW57">
+      <c r="AT57">
         <v>151.716736464092</v>
       </c>
-      <c r="AX57">
+      <c r="AU57">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -10739,24 +10220,24 @@
       <c r="AL58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO58" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP58" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ58" t="e">
-        <v>#N/A</v>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR58" t="e">
         <v>#N/A</v>
@@ -10764,19 +10245,10 @@
       <c r="AS58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV58" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW58">
+      <c r="AT58">
         <v>151.719270560305</v>
       </c>
-      <c r="AX58">
+      <c r="AU58">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -10909,24 +10381,24 @@
       <c r="AL59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP59" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ59" t="e">
-        <v>#N/A</v>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR59" t="e">
         <v>#N/A</v>
@@ -10934,19 +10406,10 @@
       <c r="AS59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW59">
+      <c r="AT59">
         <v>151.757296984696</v>
       </c>
-      <c r="AX59">
+      <c r="AU59">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -11079,24 +10542,24 @@
           <t>SG-D5BBRPI3E2F7</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO60" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP60" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ60" t="e">
-        <v>#N/A</v>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR60" t="e">
         <v>#N/A</v>
@@ -11104,19 +10567,10 @@
       <c r="AS60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV60" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW60">
+      <c r="AT60">
         <v>151.743343598915</v>
       </c>
-      <c r="AX60">
+      <c r="AU60">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -11253,24 +10707,24 @@
       <c r="AL61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO61" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP61" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ61" t="e">
-        <v>#N/A</v>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR61" t="e">
         <v>#N/A</v>
@@ -11278,19 +10732,10 @@
       <c r="AS61" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV61" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW61">
+      <c r="AT61">
         <v>151.779273244043</v>
       </c>
-      <c r="AX61">
+      <c r="AU61">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -11427,24 +10872,24 @@
       <c r="AL62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO62" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP62" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ62" t="e">
-        <v>#N/A</v>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR62" t="e">
         <v>#N/A</v>
@@ -11452,19 +10897,10 @@
       <c r="AS62" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV62" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW62">
+      <c r="AT62">
         <v>151.806500367329</v>
       </c>
-      <c r="AX62">
+      <c r="AU62">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -11607,24 +11043,24 @@
           <t>SG-010DRPI3D708</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO63" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP63" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ63" t="e">
-        <v>#N/A</v>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR63" t="e">
         <v>#N/A</v>
@@ -11632,19 +11068,10 @@
       <c r="AS63" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV63" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW63">
+      <c r="AT63">
         <v>151.681010702398</v>
       </c>
-      <c r="AX63">
+      <c r="AU63">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -11781,24 +11208,24 @@
       <c r="AL64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO64" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP64" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ64" t="e">
-        <v>#N/A</v>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR64" t="e">
         <v>#N/A</v>
@@ -11806,19 +11233,10 @@
       <c r="AS64" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV64" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW64">
+      <c r="AT64">
         <v>151.713805317914</v>
       </c>
-      <c r="AX64">
+      <c r="AU64">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -11955,24 +11373,24 @@
       <c r="AL65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AM65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO65" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP65" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ65" t="e">
-        <v>#N/A</v>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR65" t="e">
         <v>#N/A</v>
@@ -11980,19 +11398,10 @@
       <c r="AS65" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV65" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW65">
+      <c r="AT65">
         <v>151.716736464092</v>
       </c>
-      <c r="AX65">
+      <c r="AU65">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -12129,24 +11538,24 @@
       <c r="AL66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AM66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO66" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP66" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ66" t="e">
-        <v>#N/A</v>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR66" t="e">
         <v>#N/A</v>
@@ -12154,19 +11563,10 @@
       <c r="AS66" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV66" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW66">
+      <c r="AT66">
         <v>151.719270560305</v>
       </c>
-      <c r="AX66">
+      <c r="AU66">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -12301,24 +11701,24 @@
       <c r="AL67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO67" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP67" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ67" t="e">
-        <v>#N/A</v>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR67" t="e">
         <v>#N/A</v>
@@ -12326,19 +11726,10 @@
       <c r="AS67" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV67" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW67">
+      <c r="AT67">
         <v>151.757296984696</v>
       </c>
-      <c r="AX67">
+      <c r="AU67">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -12485,44 +11876,35 @@
       <c r="AL68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP68" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AQ68" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ68" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR68" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS68" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW68">
+      <c r="AT68">
         <v>151.743343598915</v>
       </c>
-      <c r="AX68">
+      <c r="AU68">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -12664,19 +12046,10 @@
       <c r="AS69" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW69">
+      <c r="AT69">
         <v>151.681010702398</v>
       </c>
-      <c r="AX69">
+      <c r="AU69">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -12811,24 +12184,24 @@
       <c r="AL70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO70" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP70" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ70" t="e">
-        <v>#N/A</v>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR70" t="e">
         <v>#N/A</v>
@@ -12836,19 +12209,10 @@
       <c r="AS70" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV70" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW70">
+      <c r="AT70">
         <v>151.779273244043</v>
       </c>
-      <c r="AX70">
+      <c r="AU70">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -12997,24 +12361,24 @@
       <c r="AL71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AM71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO71" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP71" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ71" t="e">
-        <v>#N/A</v>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR71" t="e">
         <v>#N/A</v>
@@ -13022,19 +12386,10 @@
       <c r="AS71" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV71" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW71">
+      <c r="AT71">
         <v>151.806500367329</v>
       </c>
-      <c r="AX71">
+      <c r="AU71">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -13191,44 +12546,35 @@
       <c r="AL72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO72" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP72" t="inlineStr">
         <is>
           <t>removed</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AQ72" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ72" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR72" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS72" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV72" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW72">
+      <c r="AT72">
         <v>151.681010702398</v>
       </c>
-      <c r="AX72">
+      <c r="AU72">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -13367,24 +12713,24 @@
       <c r="AL73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AM73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP73" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ73" t="e">
-        <v>#N/A</v>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR73" t="e">
         <v>#N/A</v>
@@ -13392,19 +12738,10 @@
       <c r="AS73" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW73">
+      <c r="AT73">
         <v>151.757296984696</v>
       </c>
-      <c r="AX73">
+      <c r="AU73">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -13539,24 +12876,24 @@
       <c r="AL74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AM74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP74" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ74" t="e">
-        <v>#N/A</v>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR74" t="e">
         <v>#N/A</v>
@@ -13564,19 +12901,10 @@
       <c r="AS74" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW74">
+      <c r="AT74">
         <v>151.713805317914</v>
       </c>
-      <c r="AX74">
+      <c r="AU74">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -13711,24 +13039,24 @@
       <c r="AL75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AM75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO75" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP75" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ75" t="e">
-        <v>#N/A</v>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR75" t="e">
         <v>#N/A</v>
@@ -13736,19 +13064,10 @@
       <c r="AS75" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV75" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW75">
+      <c r="AT75">
         <v>151.716736464092</v>
       </c>
-      <c r="AX75">
+      <c r="AU75">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -13883,24 +13202,24 @@
       <c r="AL76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AM76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO76" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP76" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ76" t="e">
-        <v>#N/A</v>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR76" t="e">
         <v>#N/A</v>
@@ -13908,19 +13227,10 @@
       <c r="AS76" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV76" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW76">
+      <c r="AT76">
         <v>151.719270560305</v>
       </c>
-      <c r="AX76">
+      <c r="AU76">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -14051,20 +13361,20 @@
       <c r="AL77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AM77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO77" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP77" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP77" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AQ77" t="e">
         <v>#N/A</v>
       </c>
@@ -14074,19 +13384,10 @@
       <c r="AS77" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV77" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW77">
+      <c r="AT77">
         <v>151.743343598915</v>
       </c>
-      <c r="AX77">
+      <c r="AU77">
         <v>-32.852915984434</v>
       </c>
     </row>
@@ -14221,24 +13522,24 @@
       <c r="AL78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP78" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ78" t="e">
-        <v>#N/A</v>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR78" t="e">
         <v>#N/A</v>
@@ -14246,19 +13547,10 @@
       <c r="AS78" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW78">
+      <c r="AT78">
         <v>151.779273244043</v>
       </c>
-      <c r="AX78">
+      <c r="AU78">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -14393,24 +13685,24 @@
       <c r="AL79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AM79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP79" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ79" t="e">
-        <v>#N/A</v>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR79" t="e">
         <v>#N/A</v>
@@ -14418,19 +13710,10 @@
       <c r="AS79" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW79">
+      <c r="AT79">
         <v>151.806500367329</v>
       </c>
-      <c r="AX79">
+      <c r="AU79">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -14565,24 +13848,24 @@
       <c r="AL80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AM80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO80" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP80" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ80" t="e">
-        <v>#N/A</v>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR80" t="e">
         <v>#N/A</v>
@@ -14590,19 +13873,10 @@
       <c r="AS80" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV80" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW80">
+      <c r="AT80">
         <v>151.681010702398</v>
       </c>
-      <c r="AX80">
+      <c r="AU80">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -14737,24 +14011,24 @@
       <c r="AL81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AM81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO81" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP81" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ81" t="e">
-        <v>#N/A</v>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR81" t="e">
         <v>#N/A</v>
@@ -14762,19 +14036,10 @@
       <c r="AS81" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW81">
+      <c r="AT81">
         <v>151.713805317914</v>
       </c>
-      <c r="AX81">
+      <c r="AU81">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -14909,24 +14174,24 @@
       <c r="AL82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AM82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO82" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP82" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ82" t="e">
-        <v>#N/A</v>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR82" t="e">
         <v>#N/A</v>
@@ -14934,19 +14199,10 @@
       <c r="AS82" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV82" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW82">
+      <c r="AT82">
         <v>151.716736464092</v>
       </c>
-      <c r="AX82">
+      <c r="AU82">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -15081,24 +14337,24 @@
       <c r="AL83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AM83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO83" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP83" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ83" t="e">
-        <v>#N/A</v>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR83" t="e">
         <v>#N/A</v>
@@ -15106,19 +14362,10 @@
       <c r="AS83" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV83" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW83">
+      <c r="AT83">
         <v>151.719270560305</v>
       </c>
-      <c r="AX83">
+      <c r="AU83">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -15265,24 +14512,24 @@
       <c r="AL84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AM84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO84" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP84" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ84" t="e">
-        <v>#N/A</v>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR84" t="e">
         <v>#N/A</v>
@@ -15290,19 +14537,10 @@
       <c r="AS84" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW84">
+      <c r="AT84">
         <v>151.757296984696</v>
       </c>
-      <c r="AX84">
+      <c r="AU84">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -15437,24 +14675,24 @@
       <c r="AL85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM85" t="inlineStr">
+      <c r="AM85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO85" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP85" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ85" t="e">
-        <v>#N/A</v>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR85" t="e">
         <v>#N/A</v>
@@ -15462,19 +14700,10 @@
       <c r="AS85" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV85" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW85">
+      <c r="AT85">
         <v>151.779273244043</v>
       </c>
-      <c r="AX85">
+      <c r="AU85">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -15609,24 +14838,24 @@
       <c r="AL86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AM86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO86" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP86" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ86" t="e">
-        <v>#N/A</v>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR86" t="e">
         <v>#N/A</v>
@@ -15634,19 +14863,10 @@
       <c r="AS86" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV86" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW86">
+      <c r="AT86">
         <v>151.806500367329</v>
       </c>
-      <c r="AX86">
+      <c r="AU86">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -15804,24 +15024,24 @@
       <c r="AL87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AM87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO87" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP87" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ87" t="e">
-        <v>#N/A</v>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR87" t="e">
         <v>#N/A</v>
@@ -15829,19 +15049,10 @@
       <c r="AS87" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV87" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW87">
+      <c r="AT87">
         <v>151.681010702398</v>
       </c>
-      <c r="AX87">
+      <c r="AU87">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -15980,24 +15191,24 @@
       <c r="AL88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AM88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO88" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP88" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ88" t="e">
-        <v>#N/A</v>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR88" t="e">
         <v>#N/A</v>
@@ -16005,19 +15216,10 @@
       <c r="AS88" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV88" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW88">
+      <c r="AT88">
         <v>151.713805317914</v>
       </c>
-      <c r="AX88">
+      <c r="AU88">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -16156,24 +15358,24 @@
       <c r="AL89" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AM89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO89" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP89" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ89" t="e">
-        <v>#N/A</v>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR89" t="e">
         <v>#N/A</v>
@@ -16181,19 +15383,10 @@
       <c r="AS89" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV89" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW89">
+      <c r="AT89">
         <v>151.716736464092</v>
       </c>
-      <c r="AX89">
+      <c r="AU89">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -16332,24 +15525,24 @@
       <c r="AL90" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO90" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP90" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ90" t="e">
-        <v>#N/A</v>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR90" t="e">
         <v>#N/A</v>
@@ -16357,19 +15550,10 @@
       <c r="AS90" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV90" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW90">
+      <c r="AT90">
         <v>151.719270560305</v>
       </c>
-      <c r="AX90">
+      <c r="AU90">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -16527,24 +15711,24 @@
       <c r="AL91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO91" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP91" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ91" t="e">
-        <v>#N/A</v>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR91" t="e">
         <v>#N/A</v>
@@ -16552,19 +15736,10 @@
       <c r="AS91" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV91" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW91">
+      <c r="AT91">
         <v>151.757296984696</v>
       </c>
-      <c r="AX91">
+      <c r="AU91">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -16701,24 +15876,24 @@
       <c r="AL92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AM92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO92" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP92" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ92" t="e">
-        <v>#N/A</v>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR92" t="e">
         <v>#N/A</v>
@@ -16726,19 +15901,10 @@
       <c r="AS92" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV92" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW92">
+      <c r="AT92">
         <v>151.713805317914</v>
       </c>
-      <c r="AX92">
+      <c r="AU92">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -16873,24 +16039,24 @@
       <c r="AL93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AM93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO93" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP93" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ93" t="e">
-        <v>#N/A</v>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR93" t="e">
         <v>#N/A</v>
@@ -16898,19 +16064,10 @@
       <c r="AS93" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV93" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW93">
+      <c r="AT93">
         <v>151.779273244043</v>
       </c>
-      <c r="AX93">
+      <c r="AU93">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -17045,24 +16202,24 @@
       <c r="AL94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM94" t="inlineStr">
+      <c r="AM94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO94" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP94" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ94" t="e">
-        <v>#N/A</v>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR94" t="e">
         <v>#N/A</v>
@@ -17070,19 +16227,10 @@
       <c r="AS94" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV94" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW94">
+      <c r="AT94">
         <v>151.806500367329</v>
       </c>
-      <c r="AX94">
+      <c r="AU94">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -17234,44 +16382,35 @@
       <c r="AL95" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM95" t="inlineStr">
+      <c r="AM95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO95" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP95" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
+      <c r="AQ95" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ95" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR95" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS95" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV95" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW95">
+      <c r="AT95">
         <v>151.713805317914</v>
       </c>
-      <c r="AX95">
+      <c r="AU95">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -17406,24 +16545,24 @@
       <c r="AL96" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM96" t="inlineStr">
+      <c r="AM96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO96" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP96" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ96" t="e">
-        <v>#N/A</v>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR96" t="e">
         <v>#N/A</v>
@@ -17431,19 +16570,10 @@
       <c r="AS96" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV96" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW96">
+      <c r="AT96">
         <v>151.716736464092</v>
       </c>
-      <c r="AX96">
+      <c r="AU96">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -17578,24 +16708,24 @@
       <c r="AL97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM97" t="inlineStr">
+      <c r="AM97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO97" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP97" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ97" t="e">
-        <v>#N/A</v>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR97" t="e">
         <v>#N/A</v>
@@ -17603,19 +16733,10 @@
       <c r="AS97" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV97" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW97">
+      <c r="AT97">
         <v>151.719270560305</v>
       </c>
-      <c r="AX97">
+      <c r="AU97">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -17764,24 +16885,24 @@
       <c r="AL98" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AM98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO98" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP98" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ98" t="e">
-        <v>#N/A</v>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR98" t="e">
         <v>#N/A</v>
@@ -17789,19 +16910,10 @@
       <c r="AS98" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV98" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW98">
+      <c r="AT98">
         <v>151.779273244043</v>
       </c>
-      <c r="AX98">
+      <c r="AU98">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -17940,24 +17052,24 @@
       <c r="AL99" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AM99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO99" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP99" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ99" t="e">
-        <v>#N/A</v>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR99" t="e">
         <v>#N/A</v>
@@ -17965,19 +17077,10 @@
       <c r="AS99" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV99" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW99">
+      <c r="AT99">
         <v>151.806500367329</v>
       </c>
-      <c r="AX99">
+      <c r="AU99">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -18116,24 +17219,24 @@
       <c r="AL100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO100" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP100" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ100" t="e">
-        <v>#N/A</v>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR100" t="e">
         <v>#N/A</v>
@@ -18141,19 +17244,10 @@
       <c r="AS100" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW100">
+      <c r="AT100">
         <v>151.681010702398</v>
       </c>
-      <c r="AX100">
+      <c r="AU100">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -18307,24 +17401,24 @@
       <c r="AL101" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO101" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP101" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ101" t="e">
-        <v>#N/A</v>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR101" t="e">
         <v>#N/A</v>
@@ -18332,19 +17426,10 @@
       <c r="AS101" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW101">
+      <c r="AT101">
         <v>151.713805317914</v>
       </c>
-      <c r="AX101">
+      <c r="AU101">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -18483,24 +17568,24 @@
       <c r="AL102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM102" t="inlineStr">
+      <c r="AM102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO102" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP102" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ102" t="e">
-        <v>#N/A</v>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR102" t="e">
         <v>#N/A</v>
@@ -18508,19 +17593,10 @@
       <c r="AS102" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW102">
+      <c r="AT102">
         <v>151.716736464092</v>
       </c>
-      <c r="AX102">
+      <c r="AU102">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -18659,24 +17735,24 @@
       <c r="AL103" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM103" t="inlineStr">
+      <c r="AM103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO103" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP103" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ103" t="e">
-        <v>#N/A</v>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR103" t="e">
         <v>#N/A</v>
@@ -18684,19 +17760,10 @@
       <c r="AS103" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW103">
+      <c r="AT103">
         <v>151.719270560305</v>
       </c>
-      <c r="AX103">
+      <c r="AU103">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -18852,24 +17919,24 @@
       <c r="AL104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM104" t="inlineStr">
+      <c r="AM104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO104" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP104" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ104" t="e">
-        <v>#N/A</v>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR104" t="e">
         <v>#N/A</v>
@@ -18877,19 +17944,10 @@
       <c r="AS104" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW104">
+      <c r="AT104">
         <v>151.757296984696</v>
       </c>
-      <c r="AX104">
+      <c r="AU104">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -19024,24 +18082,24 @@
       <c r="AL105" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM105" t="inlineStr">
+      <c r="AM105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO105" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP105" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ105" t="e">
-        <v>#N/A</v>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR105" t="e">
         <v>#N/A</v>
@@ -19049,19 +18107,10 @@
       <c r="AS105" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV105" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW105">
+      <c r="AT105">
         <v>152.137455181598</v>
       </c>
-      <c r="AX105">
+      <c r="AU105">
         <v>-32.684190312235</v>
       </c>
     </row>
@@ -19192,24 +18241,24 @@
           <t>SG-61F1RPI3C8AB</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
+      <c r="AM106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO106" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP106" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ106" t="e">
-        <v>#N/A</v>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR106" t="e">
         <v>#N/A</v>
@@ -19217,19 +18266,10 @@
       <c r="AS106" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV106" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW106">
+      <c r="AT106">
         <v>151.779273244043</v>
       </c>
-      <c r="AX106">
+      <c r="AU106">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -19373,19 +18413,10 @@
       <c r="AS107" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT107" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU107" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV107" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW107">
+      <c r="AT107">
         <v>151.779273244043</v>
       </c>
-      <c r="AX107">
+      <c r="AU107">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -19520,24 +18551,24 @@
       <c r="AL108" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM108" t="inlineStr">
+      <c r="AM108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO108" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP108" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ108" t="e">
-        <v>#N/A</v>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR108" t="e">
         <v>#N/A</v>
@@ -19545,19 +18576,10 @@
       <c r="AS108" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV108" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW108">
+      <c r="AT108">
         <v>151.806500367329</v>
       </c>
-      <c r="AX108">
+      <c r="AU108">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -19700,24 +18722,24 @@
       <c r="AL109" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM109" t="inlineStr">
+      <c r="AM109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO109" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP109" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ109" t="e">
-        <v>#N/A</v>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR109" t="e">
         <v>#N/A</v>
@@ -19725,19 +18747,10 @@
       <c r="AS109" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV109" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW109">
+      <c r="AT109">
         <v>151.681010702398</v>
       </c>
-      <c r="AX109">
+      <c r="AU109">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -19872,24 +18885,24 @@
       <c r="AL110" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AM110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO110" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP110" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ110" t="e">
-        <v>#N/A</v>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR110" t="e">
         <v>#N/A</v>
@@ -19897,19 +18910,10 @@
       <c r="AS110" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV110" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW110">
+      <c r="AT110">
         <v>151.716736464092</v>
       </c>
-      <c r="AX110">
+      <c r="AU110">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -20044,24 +19048,24 @@
       <c r="AL111" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AM111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO111" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP111" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ111" t="e">
-        <v>#N/A</v>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR111" t="e">
         <v>#N/A</v>
@@ -20069,19 +19073,10 @@
       <c r="AS111" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV111" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW111">
+      <c r="AT111">
         <v>151.719270560305</v>
       </c>
-      <c r="AX111">
+      <c r="AU111">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -20216,24 +19211,24 @@
       <c r="AL112" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM112" t="inlineStr">
+      <c r="AM112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO112" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP112" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ112" t="e">
-        <v>#N/A</v>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR112" t="e">
         <v>#N/A</v>
@@ -20241,19 +19236,10 @@
       <c r="AS112" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV112" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW112">
+      <c r="AT112">
         <v>151.757296984696</v>
       </c>
-      <c r="AX112">
+      <c r="AU112">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -20388,24 +19374,24 @@
       <c r="AL113" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM113" t="inlineStr">
+      <c r="AM113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO113" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP113" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ113" t="e">
-        <v>#N/A</v>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR113" t="e">
         <v>#N/A</v>
@@ -20413,19 +19399,10 @@
       <c r="AS113" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV113" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW113">
+      <c r="AT113">
         <v>151.681010702398</v>
       </c>
-      <c r="AX113">
+      <c r="AU113">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -20572,44 +19549,35 @@
       <c r="AL114" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM114" t="inlineStr">
+      <c r="AM114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO114" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP114" t="inlineStr">
         <is>
           <t>removed</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
+      <c r="AQ114" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="AO114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ114" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AR114" t="e">
         <v>#N/A</v>
       </c>
       <c r="AS114" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV114" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW114">
+      <c r="AT114">
         <v>151.713805317914</v>
       </c>
-      <c r="AX114">
+      <c r="AU114">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -20744,24 +19712,24 @@
       <c r="AL115" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AM115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO115" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP115" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ115" t="e">
-        <v>#N/A</v>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR115" t="e">
         <v>#N/A</v>
@@ -20769,19 +19737,10 @@
       <c r="AS115" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV115" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW115">
+      <c r="AT115">
         <v>151.806500367329</v>
       </c>
-      <c r="AX115">
+      <c r="AU115">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -20916,24 +19875,24 @@
       <c r="AL116" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM116" t="inlineStr">
+      <c r="AM116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO116" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP116" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ116" t="e">
-        <v>#N/A</v>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR116" t="e">
         <v>#N/A</v>
@@ -20941,19 +19900,10 @@
       <c r="AS116" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV116" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW116">
+      <c r="AT116">
         <v>151.713805317914</v>
       </c>
-      <c r="AX116">
+      <c r="AU116">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -21088,24 +20038,24 @@
       <c r="AL117" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AM117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO117" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP117" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ117" t="e">
-        <v>#N/A</v>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR117" t="e">
         <v>#N/A</v>
@@ -21113,19 +20063,10 @@
       <c r="AS117" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV117" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW117">
+      <c r="AT117">
         <v>151.716736464092</v>
       </c>
-      <c r="AX117">
+      <c r="AU117">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -21260,24 +20201,24 @@
       <c r="AL118" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM118" t="inlineStr">
+      <c r="AM118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO118" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP118" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ118" t="e">
-        <v>#N/A</v>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR118" t="e">
         <v>#N/A</v>
@@ -21285,19 +20226,10 @@
       <c r="AS118" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV118" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW118">
+      <c r="AT118">
         <v>151.719270560305</v>
       </c>
-      <c r="AX118">
+      <c r="AU118">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -21428,24 +20360,24 @@
       <c r="AL119" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM119" t="inlineStr">
+      <c r="AM119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO119" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP119" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ119" t="e">
-        <v>#N/A</v>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR119" t="e">
         <v>#N/A</v>
@@ -21453,19 +20385,10 @@
       <c r="AS119" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV119" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW119">
+      <c r="AT119">
         <v>151.757296984696</v>
       </c>
-      <c r="AX119">
+      <c r="AU119">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -21600,24 +20523,24 @@
       <c r="AL120" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM120" t="inlineStr">
+      <c r="AM120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO120" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP120" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ120" t="e">
-        <v>#N/A</v>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR120" t="e">
         <v>#N/A</v>
@@ -21625,19 +20548,10 @@
       <c r="AS120" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV120" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW120">
+      <c r="AT120">
         <v>151.779273244043</v>
       </c>
-      <c r="AX120">
+      <c r="AU120">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -21775,24 +20689,24 @@
       <c r="AL121" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM121" t="inlineStr">
+      <c r="AM121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO121" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP121" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ121" t="e">
-        <v>#N/A</v>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR121" t="e">
         <v>#N/A</v>
@@ -21800,19 +20714,10 @@
       <c r="AS121" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV121" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW121">
+      <c r="AT121">
         <v>151.969829593599</v>
       </c>
-      <c r="AX121">
+      <c r="AU121">
         <v>-32.690586398903</v>
       </c>
     </row>
@@ -21947,24 +20852,24 @@
       <c r="AL122" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM122" t="inlineStr">
+      <c r="AM122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO122" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP122" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ122" t="e">
-        <v>#N/A</v>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR122" t="e">
         <v>#N/A</v>
@@ -21972,19 +20877,10 @@
       <c r="AS122" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV122" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW122">
+      <c r="AT122">
         <v>151.779273244043</v>
       </c>
-      <c r="AX122">
+      <c r="AU122">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -22119,24 +21015,24 @@
       <c r="AL123" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM123" t="inlineStr">
+      <c r="AM123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO123" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP123" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ123" t="e">
-        <v>#N/A</v>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR123" t="e">
         <v>#N/A</v>
@@ -22144,19 +21040,10 @@
       <c r="AS123" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV123" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW123">
+      <c r="AT123">
         <v>151.806500367329</v>
       </c>
-      <c r="AX123">
+      <c r="AU123">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -22291,24 +21178,24 @@
       <c r="AL124" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM124" t="inlineStr">
+      <c r="AM124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO124" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP124" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ124" t="e">
-        <v>#N/A</v>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR124" t="e">
         <v>#N/A</v>
@@ -22316,19 +21203,10 @@
       <c r="AS124" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV124" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW124">
+      <c r="AT124">
         <v>151.681010702398</v>
       </c>
-      <c r="AX124">
+      <c r="AU124">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -22463,24 +21341,24 @@
       <c r="AL125" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM125" t="inlineStr">
+      <c r="AM125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO125" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP125" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO125" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP125" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ125" t="e">
-        <v>#N/A</v>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR125" t="e">
         <v>#N/A</v>
@@ -22488,19 +21366,10 @@
       <c r="AS125" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT125" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU125" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV125" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW125">
+      <c r="AT125">
         <v>151.713805317914</v>
       </c>
-      <c r="AX125">
+      <c r="AU125">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -22635,24 +21504,24 @@
       <c r="AL126" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM126" t="inlineStr">
+      <c r="AM126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP126" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ126" t="e">
-        <v>#N/A</v>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR126" t="e">
         <v>#N/A</v>
@@ -22660,19 +21529,10 @@
       <c r="AS126" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV126" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW126">
+      <c r="AT126">
         <v>151.716736464092</v>
       </c>
-      <c r="AX126">
+      <c r="AU126">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -22807,24 +21667,24 @@
       <c r="AL127" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM127" t="inlineStr">
+      <c r="AM127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP127" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ127" t="e">
-        <v>#N/A</v>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR127" t="e">
         <v>#N/A</v>
@@ -22832,19 +21692,10 @@
       <c r="AS127" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV127" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW127">
+      <c r="AT127">
         <v>151.719270560305</v>
       </c>
-      <c r="AX127">
+      <c r="AU127">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -22979,24 +21830,24 @@
       <c r="AL128" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM128" t="inlineStr">
+      <c r="AM128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO128" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP128" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ128" t="e">
-        <v>#N/A</v>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR128" t="e">
         <v>#N/A</v>
@@ -23004,19 +21855,10 @@
       <c r="AS128" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV128" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW128">
+      <c r="AT128">
         <v>151.757296984696</v>
       </c>
-      <c r="AX128">
+      <c r="AU128">
         <v>-32.835342462851</v>
       </c>
     </row>
@@ -23151,24 +21993,24 @@
       <c r="AL129" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM129" t="inlineStr">
+      <c r="AM129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO129" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP129" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ129" t="e">
-        <v>#N/A</v>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR129" t="e">
         <v>#N/A</v>
@@ -23176,19 +22018,10 @@
       <c r="AS129" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV129" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW129">
+      <c r="AT129">
         <v>152.137455181598</v>
       </c>
-      <c r="AX129">
+      <c r="AU129">
         <v>-32.684190312235</v>
       </c>
     </row>
@@ -23326,24 +22159,24 @@
       <c r="AL130" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM130" t="inlineStr">
+      <c r="AM130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO130" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP130" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ130" t="e">
-        <v>#N/A</v>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR130" t="e">
         <v>#N/A</v>
@@ -23351,19 +22184,10 @@
       <c r="AS130" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV130" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW130">
+      <c r="AT130">
         <v>151.969829593599</v>
       </c>
-      <c r="AX130">
+      <c r="AU130">
         <v>-32.690586398903</v>
       </c>
     </row>
@@ -23498,24 +22322,24 @@
       <c r="AL131" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM131" t="inlineStr">
+      <c r="AM131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO131" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP131" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO131" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP131" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ131" t="e">
-        <v>#N/A</v>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR131" t="e">
         <v>#N/A</v>
@@ -23523,19 +22347,10 @@
       <c r="AS131" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT131" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU131" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV131" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW131">
+      <c r="AT131">
         <v>151.779273244043</v>
       </c>
-      <c r="AX131">
+      <c r="AU131">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -23670,24 +22485,24 @@
       <c r="AL132" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM132" t="inlineStr">
+      <c r="AM132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP132" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ132" t="e">
-        <v>#N/A</v>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR132" t="e">
         <v>#N/A</v>
@@ -23695,19 +22510,10 @@
       <c r="AS132" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV132" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW132">
+      <c r="AT132">
         <v>151.806500367329</v>
       </c>
-      <c r="AX132">
+      <c r="AU132">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -23842,24 +22648,24 @@
       <c r="AL133" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM133" t="inlineStr">
+      <c r="AM133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO133" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP133" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ133" t="e">
-        <v>#N/A</v>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR133" t="e">
         <v>#N/A</v>
@@ -23867,19 +22673,10 @@
       <c r="AS133" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV133" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW133">
+      <c r="AT133">
         <v>151.681010702398</v>
       </c>
-      <c r="AX133">
+      <c r="AU133">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -24014,24 +22811,24 @@
       <c r="AL134" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM134" t="inlineStr">
+      <c r="AM134" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN134" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO134" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP134" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ134" t="e">
-        <v>#N/A</v>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR134" t="e">
         <v>#N/A</v>
@@ -24039,19 +22836,10 @@
       <c r="AS134" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV134" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW134">
+      <c r="AT134">
         <v>151.713805317914</v>
       </c>
-      <c r="AX134">
+      <c r="AU134">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -24186,24 +22974,24 @@
       <c r="AL135" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM135" t="inlineStr">
+      <c r="AM135" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN135" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO135" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP135" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ135" t="e">
-        <v>#N/A</v>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR135" t="e">
         <v>#N/A</v>
@@ -24211,19 +22999,10 @@
       <c r="AS135" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV135" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW135">
+      <c r="AT135">
         <v>151.716736464092</v>
       </c>
-      <c r="AX135">
+      <c r="AU135">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -24358,24 +23137,24 @@
       <c r="AL136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM136" t="inlineStr">
+      <c r="AM136" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN136" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO136" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP136" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO136" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP136" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ136" t="e">
-        <v>#N/A</v>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR136" t="e">
         <v>#N/A</v>
@@ -24383,19 +23162,10 @@
       <c r="AS136" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT136" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU136" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV136" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW136">
+      <c r="AT136">
         <v>151.719270560305</v>
       </c>
-      <c r="AX136">
+      <c r="AU136">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -24530,24 +23300,24 @@
       <c r="AL137" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM137" t="inlineStr">
+      <c r="AM137" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN137" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO137" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP137" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ137" t="e">
-        <v>#N/A</v>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR137" t="e">
         <v>#N/A</v>
@@ -24555,19 +23325,10 @@
       <c r="AS137" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV137" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW137">
+      <c r="AT137">
         <v>151.779273244043</v>
       </c>
-      <c r="AX137">
+      <c r="AU137">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -24702,24 +23463,24 @@
       <c r="AL138" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM138" t="inlineStr">
+      <c r="AM138" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN138" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO138" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP138" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ138" t="e">
-        <v>#N/A</v>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR138" t="e">
         <v>#N/A</v>
@@ -24727,19 +23488,10 @@
       <c r="AS138" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV138" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW138">
+      <c r="AT138">
         <v>151.806500367329</v>
       </c>
-      <c r="AX138">
+      <c r="AU138">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -24874,24 +23626,24 @@
       <c r="AL139" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM139" t="inlineStr">
+      <c r="AM139" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN139" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO139" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP139" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ139" t="e">
-        <v>#N/A</v>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR139" t="e">
         <v>#N/A</v>
@@ -24899,19 +23651,10 @@
       <c r="AS139" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV139" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW139">
+      <c r="AT139">
         <v>151.713805317914</v>
       </c>
-      <c r="AX139">
+      <c r="AU139">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -25046,24 +23789,24 @@
       <c r="AL140" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM140" t="inlineStr">
+      <c r="AM140" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN140" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO140" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP140" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ140" t="e">
-        <v>#N/A</v>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR140" t="e">
         <v>#N/A</v>
@@ -25071,19 +23814,10 @@
       <c r="AS140" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV140" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW140">
+      <c r="AT140">
         <v>151.716736464092</v>
       </c>
-      <c r="AX140">
+      <c r="AU140">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -25218,24 +23952,24 @@
       <c r="AL141" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM141" t="inlineStr">
+      <c r="AM141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO141" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP141" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ141" t="e">
-        <v>#N/A</v>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR141" t="e">
         <v>#N/A</v>
@@ -25243,19 +23977,10 @@
       <c r="AS141" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV141" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW141">
+      <c r="AT141">
         <v>151.719270560305</v>
       </c>
-      <c r="AX141">
+      <c r="AU141">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -25392,24 +24117,24 @@
       <c r="AL142" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM142" t="inlineStr">
+      <c r="AM142" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN142" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO142" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP142" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ142" t="e">
-        <v>#N/A</v>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR142" t="e">
         <v>#N/A</v>
@@ -25417,19 +24142,10 @@
       <c r="AS142" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV142" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW142">
+      <c r="AT142">
         <v>151.779273244043</v>
       </c>
-      <c r="AX142">
+      <c r="AU142">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -25564,24 +24280,24 @@
       <c r="AL143" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM143" t="inlineStr">
+      <c r="AM143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP143" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ143" t="e">
-        <v>#N/A</v>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR143" t="e">
         <v>#N/A</v>
@@ -25589,19 +24305,10 @@
       <c r="AS143" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV143" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW143">
+      <c r="AT143">
         <v>151.806500367329</v>
       </c>
-      <c r="AX143">
+      <c r="AU143">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -25736,24 +24443,24 @@
       <c r="AL144" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM144" t="inlineStr">
+      <c r="AM144" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN144" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO144" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP144" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ144" t="e">
-        <v>#N/A</v>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR144" t="e">
         <v>#N/A</v>
@@ -25761,19 +24468,10 @@
       <c r="AS144" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV144" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW144">
+      <c r="AT144">
         <v>151.713805317914</v>
       </c>
-      <c r="AX144">
+      <c r="AU144">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -25908,24 +24606,24 @@
       <c r="AL145" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM145" t="inlineStr">
+      <c r="AM145" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN145" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO145" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP145" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ145" t="e">
-        <v>#N/A</v>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR145" t="e">
         <v>#N/A</v>
@@ -25933,19 +24631,10 @@
       <c r="AS145" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV145" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW145">
+      <c r="AT145">
         <v>151.716736464092</v>
       </c>
-      <c r="AX145">
+      <c r="AU145">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -26080,24 +24769,24 @@
       <c r="AL146" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM146" t="inlineStr">
+      <c r="AM146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP146" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ146" t="e">
-        <v>#N/A</v>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR146" t="e">
         <v>#N/A</v>
@@ -26105,19 +24794,10 @@
       <c r="AS146" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV146" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW146">
+      <c r="AT146">
         <v>151.719270560305</v>
       </c>
-      <c r="AX146">
+      <c r="AU146">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -26267,19 +24947,10 @@
       <c r="AS147" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT147" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU147" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV147" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW147">
+      <c r="AT147">
         <v>151.719270560305</v>
       </c>
-      <c r="AX147">
+      <c r="AU147">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -26416,24 +25087,24 @@
       <c r="AL148" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM148" t="inlineStr">
+      <c r="AM148" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN148" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO148" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP148" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ148" t="e">
-        <v>#N/A</v>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR148" t="e">
         <v>#N/A</v>
@@ -26441,19 +25112,10 @@
       <c r="AS148" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV148" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW148">
+      <c r="AT148">
         <v>151.779273244043</v>
       </c>
-      <c r="AX148">
+      <c r="AU148">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -26588,24 +25250,24 @@
       <c r="AL149" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM149" t="inlineStr">
+      <c r="AM149" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN149" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO149" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP149" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ149" t="e">
-        <v>#N/A</v>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR149" t="e">
         <v>#N/A</v>
@@ -26613,19 +25275,10 @@
       <c r="AS149" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV149" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW149">
+      <c r="AT149">
         <v>151.806500367329</v>
       </c>
-      <c r="AX149">
+      <c r="AU149">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -26760,24 +25413,24 @@
       <c r="AL150" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM150" t="inlineStr">
+      <c r="AM150" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN150" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO150" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP150" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ150" t="e">
-        <v>#N/A</v>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR150" t="e">
         <v>#N/A</v>
@@ -26785,19 +25438,10 @@
       <c r="AS150" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV150" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW150">
+      <c r="AT150">
         <v>151.713805317914</v>
       </c>
-      <c r="AX150">
+      <c r="AU150">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -26932,24 +25576,24 @@
       <c r="AL151" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM151" t="inlineStr">
+      <c r="AM151" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN151" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO151" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP151" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ151" t="e">
-        <v>#N/A</v>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR151" t="e">
         <v>#N/A</v>
@@ -26957,19 +25601,10 @@
       <c r="AS151" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV151" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW151">
+      <c r="AT151">
         <v>151.716736464092</v>
       </c>
-      <c r="AX151">
+      <c r="AU151">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -27100,20 +25735,20 @@
       <c r="AL152" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM152" t="inlineStr">
+      <c r="AM152" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN152" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO152" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP152" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP152" t="e">
-        <v>#N/A</v>
-      </c>
       <c r="AQ152" t="e">
         <v>#N/A</v>
       </c>
@@ -27123,19 +25758,10 @@
       <c r="AS152" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV152" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW152">
+      <c r="AT152">
         <v>151.681010702398</v>
       </c>
-      <c r="AX152">
+      <c r="AU152">
         <v>-32.846728923395</v>
       </c>
     </row>
@@ -27270,24 +25896,24 @@
       <c r="AL153" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM153" t="inlineStr">
+      <c r="AM153" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN153" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO153" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP153" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ153" t="e">
-        <v>#N/A</v>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR153" t="e">
         <v>#N/A</v>
@@ -27295,19 +25921,10 @@
       <c r="AS153" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV153" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW153">
+      <c r="AT153">
         <v>151.806500367329</v>
       </c>
-      <c r="AX153">
+      <c r="AU153">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -27442,24 +26059,24 @@
       <c r="AL154" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM154" t="inlineStr">
+      <c r="AM154" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN154" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO154" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP154" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ154" t="e">
-        <v>#N/A</v>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR154" t="e">
         <v>#N/A</v>
@@ -27467,19 +26084,10 @@
       <c r="AS154" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV154" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW154">
+      <c r="AT154">
         <v>151.713805317914</v>
       </c>
-      <c r="AX154">
+      <c r="AU154">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -27614,24 +26222,24 @@
       <c r="AL155" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM155" t="inlineStr">
+      <c r="AM155" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN155" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO155" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP155" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ155" t="e">
-        <v>#N/A</v>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR155" t="e">
         <v>#N/A</v>
@@ -27639,19 +26247,10 @@
       <c r="AS155" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV155" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW155">
+      <c r="AT155">
         <v>151.716736464092</v>
       </c>
-      <c r="AX155">
+      <c r="AU155">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -27786,24 +26385,24 @@
       <c r="AL156" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM156" t="inlineStr">
+      <c r="AM156" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN156" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO156" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP156" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ156" t="e">
-        <v>#N/A</v>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR156" t="e">
         <v>#N/A</v>
@@ -27811,19 +26410,10 @@
       <c r="AS156" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV156" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW156">
+      <c r="AT156">
         <v>151.806500367329</v>
       </c>
-      <c r="AX156">
+      <c r="AU156">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -27958,24 +26548,24 @@
       <c r="AL157" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM157" t="inlineStr">
+      <c r="AM157" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN157" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO157" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP157" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ157" t="e">
-        <v>#N/A</v>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR157" t="e">
         <v>#N/A</v>
@@ -27983,19 +26573,10 @@
       <c r="AS157" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV157" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW157">
+      <c r="AT157">
         <v>151.713805317914</v>
       </c>
-      <c r="AX157">
+      <c r="AU157">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -28130,24 +26711,24 @@
       <c r="AL158" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM158" t="inlineStr">
+      <c r="AM158" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN158" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO158" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP158" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ158" t="e">
-        <v>#N/A</v>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR158" t="e">
         <v>#N/A</v>
@@ -28155,19 +26736,10 @@
       <c r="AS158" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV158" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW158">
+      <c r="AT158">
         <v>151.716736464092</v>
       </c>
-      <c r="AX158">
+      <c r="AU158">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -28304,24 +26876,24 @@
       <c r="AL159" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM159" t="inlineStr">
+      <c r="AM159" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN159" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO159" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP159" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ159" t="e">
-        <v>#N/A</v>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR159" t="e">
         <v>#N/A</v>
@@ -28329,19 +26901,10 @@
       <c r="AS159" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV159" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW159">
+      <c r="AT159">
         <v>151.806500367329</v>
       </c>
-      <c r="AX159">
+      <c r="AU159">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -28478,24 +27041,24 @@
       <c r="AL160" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM160" t="inlineStr">
+      <c r="AM160" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN160" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO160" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP160" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO160" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP160" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ160" t="e">
-        <v>#N/A</v>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR160" t="e">
         <v>#N/A</v>
@@ -28503,19 +27066,10 @@
       <c r="AS160" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT160" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU160" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV160" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW160">
+      <c r="AT160">
         <v>151.713805317914</v>
       </c>
-      <c r="AX160">
+      <c r="AU160">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -28652,24 +27206,24 @@
       <c r="AL161" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM161" t="inlineStr">
+      <c r="AM161" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN161" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO161" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP161" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO161" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP161" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ161" t="e">
-        <v>#N/A</v>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR161" t="e">
         <v>#N/A</v>
@@ -28677,19 +27231,10 @@
       <c r="AS161" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT161" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU161" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV161" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW161">
+      <c r="AT161">
         <v>151.716736464092</v>
       </c>
-      <c r="AX161">
+      <c r="AU161">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -28824,24 +27369,24 @@
       <c r="AL162" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM162" t="inlineStr">
+      <c r="AM162" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN162" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO162" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP162" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ162" t="e">
-        <v>#N/A</v>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR162" t="e">
         <v>#N/A</v>
@@ -28849,19 +27394,10 @@
       <c r="AS162" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV162" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW162">
+      <c r="AT162">
         <v>151.806500367329</v>
       </c>
-      <c r="AX162">
+      <c r="AU162">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -28996,24 +27532,24 @@
       <c r="AL163" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM163" t="inlineStr">
+      <c r="AM163" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN163" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO163" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP163" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ163" t="e">
-        <v>#N/A</v>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR163" t="e">
         <v>#N/A</v>
@@ -29021,19 +27557,10 @@
       <c r="AS163" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV163" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW163">
+      <c r="AT163">
         <v>151.713805317914</v>
       </c>
-      <c r="AX163">
+      <c r="AU163">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -29168,24 +27695,24 @@
       <c r="AL164" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM164" t="inlineStr">
+      <c r="AM164" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN164" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO164" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP164" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ164" t="e">
-        <v>#N/A</v>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR164" t="e">
         <v>#N/A</v>
@@ -29193,19 +27720,10 @@
       <c r="AS164" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV164" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW164">
+      <c r="AT164">
         <v>151.716736464092</v>
       </c>
-      <c r="AX164">
+      <c r="AU164">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -29340,24 +27858,24 @@
       <c r="AL165" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM165" t="inlineStr">
+      <c r="AM165" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN165" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO165" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP165" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ165" t="e">
-        <v>#N/A</v>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR165" t="e">
         <v>#N/A</v>
@@ -29365,19 +27883,10 @@
       <c r="AS165" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV165" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW165">
+      <c r="AT165">
         <v>151.719270560305</v>
       </c>
-      <c r="AX165">
+      <c r="AU165">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -29512,24 +28021,24 @@
       <c r="AL166" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM166" t="inlineStr">
+      <c r="AM166" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN166" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO166" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP166" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ166" t="e">
-        <v>#N/A</v>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR166" t="e">
         <v>#N/A</v>
@@ -29537,19 +28046,10 @@
       <c r="AS166" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV166" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW166">
+      <c r="AT166">
         <v>151.806500367329</v>
       </c>
-      <c r="AX166">
+      <c r="AU166">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -29684,24 +28184,24 @@
       <c r="AL167" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM167" t="inlineStr">
+      <c r="AM167" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN167" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO167" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP167" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ167" t="e">
-        <v>#N/A</v>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR167" t="e">
         <v>#N/A</v>
@@ -29709,19 +28209,10 @@
       <c r="AS167" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV167" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW167">
+      <c r="AT167">
         <v>151.713805317914</v>
       </c>
-      <c r="AX167">
+      <c r="AU167">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -29856,24 +28347,24 @@
       <c r="AL168" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM168" t="inlineStr">
+      <c r="AM168" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN168" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO168" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP168" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ168" t="e">
-        <v>#N/A</v>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR168" t="e">
         <v>#N/A</v>
@@ -29881,19 +28372,10 @@
       <c r="AS168" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV168" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW168">
+      <c r="AT168">
         <v>151.716736464092</v>
       </c>
-      <c r="AX168">
+      <c r="AU168">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -30028,24 +28510,24 @@
       <c r="AL169" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM169" t="inlineStr">
+      <c r="AM169" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN169" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO169" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP169" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ169" t="e">
-        <v>#N/A</v>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR169" t="e">
         <v>#N/A</v>
@@ -30053,19 +28535,10 @@
       <c r="AS169" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV169" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW169">
+      <c r="AT169">
         <v>151.719270560305</v>
       </c>
-      <c r="AX169">
+      <c r="AU169">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -30200,24 +28673,24 @@
       <c r="AL170" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM170" t="inlineStr">
+      <c r="AM170" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN170" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO170" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP170" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO170" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP170" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ170" t="e">
-        <v>#N/A</v>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR170" t="e">
         <v>#N/A</v>
@@ -30225,19 +28698,10 @@
       <c r="AS170" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT170" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU170" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV170" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW170">
+      <c r="AT170">
         <v>151.806500367329</v>
       </c>
-      <c r="AX170">
+      <c r="AU170">
         <v>-32.847730243287</v>
       </c>
     </row>
@@ -30372,24 +28836,24 @@
       <c r="AL171" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM171" t="inlineStr">
+      <c r="AM171" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN171" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO171" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP171" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ171" t="e">
-        <v>#N/A</v>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR171" t="e">
         <v>#N/A</v>
@@ -30397,19 +28861,10 @@
       <c r="AS171" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV171" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW171">
+      <c r="AT171">
         <v>151.713805317914</v>
       </c>
-      <c r="AX171">
+      <c r="AU171">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -30544,24 +28999,24 @@
       <c r="AL172" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM172" t="inlineStr">
+      <c r="AM172" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN172" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO172" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP172" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ172" t="e">
-        <v>#N/A</v>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR172" t="e">
         <v>#N/A</v>
@@ -30569,19 +29024,10 @@
       <c r="AS172" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV172" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW172">
+      <c r="AT172">
         <v>151.716736464092</v>
       </c>
-      <c r="AX172">
+      <c r="AU172">
         <v>-32.869522196145</v>
       </c>
     </row>
@@ -30716,24 +29162,24 @@
       <c r="AL173" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM173" t="inlineStr">
+      <c r="AM173" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN173" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO173" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP173" t="inlineStr">
         <is>
           <t>on</t>
         </is>
       </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AO173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ173" t="e">
-        <v>#N/A</v>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
       <c r="AR173" t="e">
         <v>#N/A</v>
@@ -30741,19 +29187,10 @@
       <c r="AS173" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV173" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW173">
+      <c r="AT173">
         <v>151.719270560305</v>
       </c>
-      <c r="AX173">
+      <c r="AU173">
         <v>-32.860196358204</v>
       </c>
     </row>
@@ -30895,19 +29332,10 @@
       <c r="AS174" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT174" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU174" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV174" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW174">
+      <c r="AT174">
         <v>151.779273244043</v>
       </c>
-      <c r="AX174">
+      <c r="AU174">
         <v>-32.874694481161</v>
       </c>
     </row>
@@ -31051,19 +29479,10 @@
       <c r="AS175" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT175" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU175" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV175" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW175">
+      <c r="AT175">
         <v>151.713805317914</v>
       </c>
-      <c r="AX175">
+      <c r="AU175">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -31186,46 +29605,37 @@
       <c r="AL176" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AM176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP176" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AN176" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
         <is>
           <t>(This note is intended for the real-time tag test): Live tags detected on both old and new receiver</t>
         </is>
       </c>
+      <c r="AP176" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ176" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR176" t="e">
+        <v>#N/A</v>
+      </c>
       <c r="AS176" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV176" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW176">
+      <c r="AT176">
         <v>151.713805317914</v>
       </c>
-      <c r="AX176">
+      <c r="AU176">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -31369,19 +29779,10 @@
       <c r="AS177" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT177" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU177" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV177" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW177">
+      <c r="AT177">
         <v>151.713805317914</v>
       </c>
-      <c r="AX177">
+      <c r="AU177">
         <v>-32.844956260503</v>
       </c>
     </row>
@@ -31525,19 +29926,10 @@
       <c r="AS178" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AT178" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU178" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV178" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW178">
+      <c r="AT178">
         <v>151.713805317914</v>
       </c>
-      <c r="AX178">
+      <c r="AU178">
         <v>-32.844956260503</v>
       </c>
     </row>

--- a/docs/qmd/chapter_1/downloads/receiver_log_complete.xlsx
+++ b/docs/qmd/chapter_1/downloads/receiver_log_complete.xlsx
@@ -621,7 +621,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SG-7F7ERPI3I522</t>
+          <t>SG-7F7ERPI31522</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SG-3315RPI33AD3</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SG-3315RPI33AD3</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SG-E3E4RPI4CE25</t>
+          <t>SG-E3E4RPI4CED5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
